--- a/TestData/DeviceConfig.xlsx
+++ b/TestData/DeviceConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Paresh automation\Titan-Mobile-Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48B8047F-FECC-4063-B5C4-FABCE3C44121}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF40B2E8-746A-4895-89B5-065461622DE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6000" yWindow="4125" windowWidth="14490" windowHeight="6795" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Devices" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="11">
   <si>
     <t>DeviceName</t>
   </si>
@@ -48,9 +48,6 @@
     <t>14.0</t>
   </si>
   <si>
-    <t>8698294937</t>
-  </si>
-  <si>
     <t>254265</t>
   </si>
   <si>
@@ -58,6 +55,9 @@
   </si>
   <si>
     <t>Google Pixel 8</t>
+  </si>
+  <si>
+    <t>N</t>
   </si>
 </sst>
 </file>
@@ -415,7 +415,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.28515625" bestFit="1" customWidth="1"/>
@@ -449,31 +449,48 @@
       <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2">
+        <v>8412365635</v>
+      </c>
+      <c r="D2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>8</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>6</v>
       </c>
       <c r="C3">
-        <v>8779906355</v>
+        <v>7897654545</v>
       </c>
       <c r="D3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" t="s">
         <v>8</v>
       </c>
-      <c r="E3" t="s">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>6873574152</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
